--- a/result/cluster_analysis.xlsx
+++ b/result/cluster_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="B1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,390 +455,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>788</v>
-      </c>
-      <c r="B2" t="n">
-        <v>8.86213207244873</v>
-      </c>
-      <c r="C2" t="n">
-        <v>8.4439697265625</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>AF-P54854-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>83.92322751322752</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>YDL245C</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>798</v>
-      </c>
-      <c r="B3" t="n">
-        <v>8.88664722442627</v>
-      </c>
-      <c r="C3" t="n">
-        <v>8.468592643737793</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AF-P13181-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>82.94155052264807</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>YLR081W</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>836</v>
-      </c>
-      <c r="B4" t="n">
-        <v>8.886992454528809</v>
-      </c>
-      <c r="C4" t="n">
-        <v>8.483911514282227</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AF-P32465-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>84.33254385964912</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>YHR094C</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>1010</v>
-      </c>
-      <c r="B5" t="n">
-        <v>8.847356796264648</v>
-      </c>
-      <c r="C5" t="n">
-        <v>8.426175117492676</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AF-P43581-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>85.83452380952382</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>YFL011W</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>1035</v>
-      </c>
-      <c r="B6" t="n">
-        <v>8.849462509155273</v>
-      </c>
-      <c r="C6" t="n">
-        <v>8.42772102355957</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>AF-P47185-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>84.00082892416226</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>YJR158W</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>1167</v>
-      </c>
-      <c r="B7" t="n">
-        <v>8.848146438598633</v>
-      </c>
-      <c r="C7" t="n">
-        <v>8.427236557006836</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>AF-P53631-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>84.80127659574468</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>YNR072W</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>1476</v>
-      </c>
-      <c r="B8" t="n">
-        <v>8.88752269744873</v>
-      </c>
-      <c r="C8" t="n">
-        <v>8.47026252746582</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>AF-P40885-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>83.48209876543211</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>YJL219W</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>2324</v>
-      </c>
-      <c r="B9" t="n">
-        <v>8.884705543518066</v>
-      </c>
-      <c r="C9" t="n">
-        <v>8.466276168823242</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>AF-P39003-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>84.12873684210527</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>YDR343C</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>2498</v>
-      </c>
-      <c r="B10" t="n">
-        <v>8.878420829772949</v>
-      </c>
-      <c r="C10" t="n">
-        <v>8.459940910339355</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>AF-P23585-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>86.7468022181146</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>YMR011W</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>2644</v>
-      </c>
-      <c r="B11" t="n">
-        <v>8.884756088256836</v>
-      </c>
-      <c r="C11" t="n">
-        <v>8.466982841491699</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>AF-P32466-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>84.6420987654321</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>YDR345C</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>2800</v>
-      </c>
-      <c r="B12" t="n">
-        <v>8.894935607910156</v>
-      </c>
-      <c r="C12" t="n">
-        <v>8.477604866027832</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>AF-P54862-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>82.9936507936508</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>YOL156W</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>3102</v>
-      </c>
-      <c r="B13" t="n">
-        <v>8.88325309753418</v>
-      </c>
-      <c r="C13" t="n">
-        <v>8.465250015258789</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>AF-P39004-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>83.10842105263158</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>YDR342C</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>3226</v>
-      </c>
-      <c r="B14" t="n">
-        <v>8.885369300842285</v>
-      </c>
-      <c r="C14" t="n">
-        <v>8.465818405151367</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>AF-P38695-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>82.6806418918919</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>YHR096C</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>3730</v>
-      </c>
-      <c r="B15" t="n">
-        <v>8.868001937866211</v>
-      </c>
-      <c r="C15" t="n">
-        <v>8.450043678283691</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>AF-P39924-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>84.14921985815603</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>YEL069C</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>4145</v>
-      </c>
-      <c r="B16" t="n">
-        <v>8.879655838012695</v>
-      </c>
-      <c r="C16" t="n">
-        <v>8.461250305175781</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>AF-P40886-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>79.85425307557118</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>YJL214W</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>4163</v>
-      </c>
-      <c r="B17" t="n">
-        <v>8.88667106628418</v>
-      </c>
-      <c r="C17" t="n">
-        <v>8.468472480773926</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>AF-P32467-F1-model_v1.pdb</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>82.74473958333334</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>YHR092C</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
